--- a/Result/profitability/1423.xlsx
+++ b/Result/profitability/1423.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6287500000000001</v>
+        <v>0.6212500000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>-19.0925</v>
+        <v>-15.79875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.17</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5675</v>
+        <v>0.5737500000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>-16.225</v>
+        <v>-10.35375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.06</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5337500000000001</v>
+        <v>0.47375</v>
       </c>
       <c r="N4" t="n">
-        <v>-10.76875</v>
+        <v>-10.83375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3150000000000001</v>
+        <v>0.27</v>
       </c>
       <c r="N5" t="n">
-        <v>-17.85</v>
+        <v>-1.29875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>-0.06</v>
       </c>
       <c r="M6" t="n">
-        <v>0.23</v>
+        <v>-0.07500000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.895000000000001</v>
+        <v>-7.7025</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.16</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.08749999999999998</v>
+        <v>-0.09250000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>-4.536250000000001</v>
+        <v>-2.74</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.15</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.10625</v>
+        <v>-0.0925</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7525000000000004</v>
+        <v>-4.06</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>-0.125</v>
       </c>
       <c r="N10" t="n">
-        <v>-3.142500000000001</v>
+        <v>-3.1425</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -2026,7 +2026,7 @@
         <v>-0.01</v>
       </c>
       <c r="M13" t="n">
-        <v>0.02375000000000002</v>
+        <v>0.02375</v>
       </c>
       <c r="N13" t="n">
         <v>5.837499999999999</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1423</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>13</v>
+      </c>
+      <c r="D75" t="n">
+        <v>13</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-63.88%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>35</v>
+      </c>
+      <c r="J75" t="n">
+        <v>26</v>
+      </c>
+      <c r="K75" t="n">
+        <v>26</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.6625000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-19.7125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.7333333333333334</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-26.46</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-1.055023923444976</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.5806451612903225</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>132.41</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.9896853277524479</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
